--- a/research/fasih-dashboard-se2026/data_mikro_sls/tabulasi_agregat_kecamatan.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/tabulasi_agregat_kecamatan.xlsx
@@ -27,13 +27,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -44,7 +47,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -52,12 +55,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,177 +439,177 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Prelist Usaha &amp; Keluarga</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Responden Didata</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Persentase Responden Didata</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Responden Sedang Didata (DRAFT)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Persentase Responden Sedang Didata (DRAFT)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Diff_Target_Pencacah</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Diff_Realisasi_Pencacah</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Diff_Target_Pengawas</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Diff_Realisasi_Pengawas</t>
         </is>
@@ -2394,172 +2406,172 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Tinggal Bersama Keluarga</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Anggota Keluarga Baru</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Meninggal</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Pindah Dalam Negeri (DN)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Pindah Luar Negeri (LN)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Tidak Ditemukan</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Anggota Keluarga Khusus</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Total Anggota Keluarga ((3) + (4))</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
@@ -4200,147 +4212,147 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>PENDATAAN K1 - Jumlah Bangunan Keluarga Khusus Hasil Pendataan PPL</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>PENDATAAN K1 - Jumlah Bangunan Keluarga Khusus Didata</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Persentase Bangunan Keluarga Khusus Didata</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
@@ -5756,192 +5768,192 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH PRELIST - UB</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH PRELIST - UM</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH PRELIST - UMK</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH PRELIST - Jumlah Prelist Usaha</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH DIDATA - UB​</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH DIDATA - Persentase UB​</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH DIDATA - UM​</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH DIDATA - Persentase UM​</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH DIDATA - UMK​</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH DIDATA - Persentase UMK​</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH DIDATA - Total Usaha</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH DIDATA - Persentase Total Usaha</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
@@ -7882,197 +7894,197 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Prelist Usaha</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Ditemukan</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Persentase Ditemukan</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Tutup</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Persentase Tutup</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Ganda</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Persentase Ganda</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Tidak Ditemukan</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Persentase Tidak Ditemukan</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Baru</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Persentase Baru</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Usaha BKU</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Persentase Usaha BKU</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
@@ -10061,162 +10073,162 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Ditemukan</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Tutup</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Ganda</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Tidak Ditemukan</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Baru</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Usaha dalam Keluarga</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
@@ -11869,197 +11881,197 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Prelist Usaha</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Prelist Usaha Keluarga (ST2023 + UMKM)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>USAHA BKU - Ditemukan</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>USAHA BKU - Persentase Ditemukan</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>USAHA BKU - Baru</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>USAHA BKU - Persentase Baru</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>USAHA BKU - subtotal</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA - Ditemukan​</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA - Persentase Ditemukan​</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA - Baru​</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA - Persentase Baru​</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA - subtotal​</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Total Usaha</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
@@ -14048,157 +14060,157 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Usaha (semua status keberadaan usaha)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Usaha BKU</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Persentase Usaha BKU</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Usaha Dalam Keluarga</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Persentase Usaha Dalam Keluarga</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
@@ -15803,162 +15815,162 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BERDASARKAN JARINGAN USAHA - Tunggal</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BERDASARKAN JARINGAN USAHA - Kantor Pusat</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BERDASARKAN JARINGAN USAHA - Cabang</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BERDASARKAN JARINGAN USAHA - Perwakilan</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BERDASARKAN JARINGAN USAHA - Pabrik</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BERDASARKAN JARINGAN USAHA - Unit Pembantu</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
@@ -17611,207 +17623,207 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Prelist Usaha SE2026</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Jumlah UTP Subsektor Target (ST2023)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Jumlah UTP Subsektor Prelist</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>USAHA DITEMUKAN - Pertanian</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>USAHA DITEMUKAN - Persentase Pertanian</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>USAHA DITEMUKAN - Non Pertanian</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>USAHA BARU - Pertanian​</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>USAHA BARU - Persentase Pertanian​</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>USAHA BARU - Non Pertanian​</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA DITEMUKAN - Pertanian​​</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA DITEMUKAN - Persentase Pertanian​​</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA DITEMUKAN - Non Pertanian​​</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA BARU - Pertanian​​​</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA BARU - Persentase Pertanian​​​</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA BARU - Non Pertanian​​​</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
@@ -19896,222 +19908,222 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Prelist Awal</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Ditemukan</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Persentase Ditemukan</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Keluarga Baru</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Meninggal</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Persentase Meninggal</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Tidak Eligible</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Persentase Tidak Eligible</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Tidak Dapat Ditemui Sampai Akhir Pendataan</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Persentase Tidak Dapat Ditemui Sampai Akhir Pendataan</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Tidak Ditemukan</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Persentase Tidak Ditemukan</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Total Hasil Pendataan ((4) + (5))</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Persentase Total Hasil Pendataan ((4) + (5))</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Diff_Target_Pencacah</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Diff_Realisasi_Pencacah</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Diff_Target_Pengawas</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Diff_Realisasi_Pengawas</t>
         </is>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/tabulasi_agregat_kecamatan.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/tabulasi_agregat_kecamatan.xlsx
@@ -27,16 +27,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -47,7 +44,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -55,21 +52,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -439,177 +427,177 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Jumlah Prelist Usaha &amp; Keluarga</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Jumlah Responden Didata</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Persentase Responden Didata</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Jumlah Responden Sedang Didata (DRAFT)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Persentase Responden Sedang Didata (DRAFT)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Diff_Target_Pencacah</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Diff_Realisasi_Pencacah</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Diff_Target_Pengawas</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Diff_Realisasi_Pengawas</t>
         </is>
@@ -2406,172 +2394,172 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Tinggal Bersama Keluarga</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Anggota Keluarga Baru</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Meninggal</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Pindah Dalam Negeri (DN)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Pindah Luar Negeri (LN)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Tidak Ditemukan</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Anggota Keluarga Khusus</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Total Anggota Keluarga ((3) + (4))</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
@@ -4212,147 +4200,147 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PENDATAAN K1 - Jumlah Bangunan Keluarga Khusus Hasil Pendataan PPL</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>PENDATAAN K1 - Jumlah Bangunan Keluarga Khusus Didata</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Persentase Bangunan Keluarga Khusus Didata</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
@@ -5768,192 +5756,192 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>JUMLAH PRELIST - UB</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>JUMLAH PRELIST - UM</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>JUMLAH PRELIST - UMK</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>JUMLAH PRELIST - Jumlah Prelist Usaha</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>JUMLAH DIDATA - UB​</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>JUMLAH DIDATA - Persentase UB​</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>JUMLAH DIDATA - UM​</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>JUMLAH DIDATA - Persentase UM​</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>JUMLAH DIDATA - UMK​</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>JUMLAH DIDATA - Persentase UMK​</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>JUMLAH DIDATA - Total Usaha</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>JUMLAH DIDATA - Persentase Total Usaha</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
@@ -7894,197 +7882,197 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Jumlah Prelist Usaha</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Ditemukan</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Persentase Ditemukan</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Tutup</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Persentase Tutup</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Ganda</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Persentase Ganda</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Tidak Ditemukan</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Persentase Tidak Ditemukan</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Baru</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BKU MENURUT STATUS KEBERADAAN USAHA - Persentase Baru</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Jumlah Usaha BKU</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Persentase Usaha BKU</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
@@ -10073,162 +10061,162 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Ditemukan</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Tutup</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Ganda</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Tidak Ditemukan</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Baru</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Jumlah Usaha dalam Keluarga</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
@@ -11881,197 +11869,197 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Jumlah Prelist Usaha</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Jumlah Prelist Usaha Keluarga (ST2023 + UMKM)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>USAHA BKU - Ditemukan</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>USAHA BKU - Persentase Ditemukan</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>USAHA BKU - Baru</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>USAHA BKU - Persentase Baru</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>USAHA BKU - subtotal</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA - Ditemukan​</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA - Persentase Ditemukan​</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA - Baru​</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA - Persentase Baru​</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA - subtotal​</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Total Usaha</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
@@ -14060,157 +14048,157 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Jumlah Usaha (semua status keberadaan usaha)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Jumlah Usaha BKU</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Persentase Usaha BKU</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Jumlah Usaha Dalam Keluarga</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Persentase Usaha Dalam Keluarga</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
@@ -15815,162 +15803,162 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BERDASARKAN JARINGAN USAHA - Tunggal</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BERDASARKAN JARINGAN USAHA - Kantor Pusat</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BERDASARKAN JARINGAN USAHA - Cabang</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BERDASARKAN JARINGAN USAHA - Perwakilan</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BERDASARKAN JARINGAN USAHA - Pabrik</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA BERDASARKAN JARINGAN USAHA - Unit Pembantu</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
@@ -17623,207 +17611,207 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Jumlah Prelist Usaha SE2026</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Jumlah UTP Subsektor Target (ST2023)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Jumlah UTP Subsektor Prelist</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>USAHA DITEMUKAN - Pertanian</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>USAHA DITEMUKAN - Persentase Pertanian</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>USAHA DITEMUKAN - Non Pertanian</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>USAHA BARU - Pertanian​</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>USAHA BARU - Persentase Pertanian​</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>USAHA BARU - Non Pertanian​</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA DITEMUKAN - Pertanian​​</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA DITEMUKAN - Persentase Pertanian​​</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA DITEMUKAN - Non Pertanian​​</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA BARU - Pertanian​​​</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA BARU - Persentase Pertanian​​​</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA BARU - Non Pertanian​​​</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
@@ -19908,222 +19896,222 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Prelist Awal</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Ditemukan</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Persentase Ditemukan</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Keluarga Baru</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Meninggal</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Persentase Meninggal</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Tidak Eligible</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Persentase Tidak Eligible</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Tidak Dapat Ditemui Sampai Akhir Pendataan</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Persentase Tidak Dapat Ditemui Sampai Akhir Pendataan</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Tidak Ditemukan</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Persentase Tidak Ditemukan</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Total Hasil Pendataan ((4) + (5))</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Persentase Total Hasil Pendataan ((4) + (5))</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Diff_Target_Pencacah</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Diff_Realisasi_Pencacah</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Diff_Target_Pengawas</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Diff_Realisasi_Pengawas</t>
         </is>
